--- a/outputs/daily/predictions_2026-06-27.xlsx
+++ b/outputs/daily/predictions_2026-06-27.xlsx
@@ -843,100 +843,100 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7999870618647504</v>
+        <v>0.8361580315263535</v>
       </c>
       <c r="L2" t="n">
-        <v>2.391457146393692</v>
+        <v>2.387025033775027</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05834015272781402</v>
+        <v>0.05614718560802987</v>
       </c>
       <c r="O2" t="n">
-        <v>0.113264793393054</v>
+        <v>0.107762956772544</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8283950538791318</v>
+        <v>0.8360898576194261</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6691348728246319</v>
+        <v>0.6726905322487416</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7512887370630403</v>
+        <v>0.7491853501406098</v>
       </c>
       <c r="S2" t="n">
-        <v>2.69871126293696</v>
+        <v>2.72081464985939</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1204439464766267</v>
+        <v>0.1215319016822887</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1633778503927175</v>
+        <v>0.1695073238852264</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7161782031306558</v>
+        <v>0.7089607744324848</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5343200176876705</v>
+        <v>0.5225983491535802</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4550329178926148</v>
+        <v>0.433298184472925</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09884772820396272</v>
+        <v>0.1051751060961755</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1821532329797396</v>
+        <v>0.1848814905131501</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7189990388162975</v>
+        <v>0.7099434033906745</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6182918628192435</v>
+        <v>0.6248981798701336</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3817081371807565</v>
+        <v>0.3751018201298664</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5081450050682195</v>
+        <v>0.5225006599818274</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4918549949317805</v>
+        <v>0.4774993400181726</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.097945</v>
+        <v>0.10509</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.182595</v>
+        <v>0.184465</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.71946</v>
+        <v>0.710445</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.617445</v>
+        <v>0.624015</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.50865</v>
+        <v>0.52197</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.79994</v>
+        <v>0.836385</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.39296</v>
+        <v>2.387305</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.1929</v>
+        <v>3.22369</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.09020337440893562</v>
+        <v>0.09128881635605689</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1480264732396076</v>
+        <v>0.1486531186971344</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.7617701523514568</v>
+        <v>0.7600580649468088</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.7617701523514568</v>
+        <v>0.7600580649468088</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>17.14085331016358</v>
+        <v>17.81033170533458</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09020337440893562</v>
+        <v>0.09128881635605689</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.03186322168112159</v>
+        <v>0.03514163074802702</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.5461628088253292</v>
+        <v>0.6258841002887463</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3.022379567581237</v>
+        <v>3.055212569530554</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.3817081371807565</v>
+        <v>0.3751018201298664</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05084301000538832</v>
+        <v>0.04779235237860807</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1536668745946141</v>
+        <v>0.1460157957145569</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.1175673454603743</v>
+        <v>0.1134726373073162</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.09405235526608295</v>
+        <v>0.09488105704298941</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1005,23 +1005,23 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>0.0937190894945827</v>
+        <v>0.09028734196701264</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.08744706173628256</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BK2" t="n">
-        <v>0.09045707559248892</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
       <c r="BM2" t="n">
-        <v>0.08652263825735276</v>
+        <v>0.08712479352473995</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>0.07497405904541082</v>
+        <v>0.07549448613088403</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.05603129658133243</v>
+        <v>0.05387953637706643</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.04897986200981023</v>
+        <v>0.0477794477245535</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.04482431232457258</v>
+        <v>0.04505180707660041</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.03762033367538668</v>
+        <v>0.03966777894310284</v>
       </c>
     </row>
     <row r="3">
@@ -1114,100 +1114,100 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6837245609322</v>
+        <v>1.71180933510296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8127268399677544</v>
+        <v>0.8378504036429046</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5072017770380104</v>
+        <v>0.5209911610371463</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3040631369785223</v>
+        <v>0.3013824996318002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1887350859834673</v>
+        <v>0.1776263393310534</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4024854736971278</v>
+        <v>0.3892935629068074</v>
       </c>
       <c r="R3" t="n">
-        <v>1.485575197853873</v>
+        <v>1.47780608139689</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8044248021461268</v>
+        <v>0.7621939186031105</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6482393810018844</v>
+        <v>0.6412021626191222</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2070479216490695</v>
+        <v>0.2111213588068991</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1447126973490462</v>
+        <v>0.1476764785739787</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5266003277704718</v>
+        <v>0.5144550869130842</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4844374384340105</v>
+        <v>0.4709048061239228</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5696722250943442</v>
+        <v>0.5699968054972755</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2626042174440482</v>
+        <v>0.2597171969048454</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1677235574616077</v>
+        <v>0.1702859975978795</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4552753829239403</v>
+        <v>0.4688596511293709</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5447246170760598</v>
+        <v>0.5311403488706291</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4643213901286803</v>
+        <v>0.4761322910343838</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5356786098713198</v>
+        <v>0.5238677089656163</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.57059</v>
+        <v>0.57117</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.261275</v>
+        <v>0.258375</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.168135</v>
+        <v>0.170455</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.45515</v>
+        <v>0.46853</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.462985</v>
+        <v>0.47469</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.6846</v>
+        <v>1.71252</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8112</v>
+        <v>0.83675</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.4958</v>
+        <v>2.54927</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.5721825504394498</v>
+        <v>0.5753164227058701</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2597430817295953</v>
+        <v>0.2593747746613462</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.168074367830955</v>
+        <v>0.1653088026327838</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.5721825504394498</v>
+        <v>0.5753164227058701</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,49 +1226,49 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2.484561718002535</v>
+        <v>2.5687555492393</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4552753829239403</v>
+        <v>0.4688596511293709</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.05278990922681243</v>
+        <v>0.0795660882225635</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1311597875617669</v>
+        <v>0.2043858306529738</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OVER_2_5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1.971601925056068</v>
+        <v>2.5687555492393</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.5721825504394498</v>
+        <v>0.4688596511293709</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.06498077340143937</v>
+        <v>0.0795660882225635</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.12811621792991</v>
+        <v>0.2043858306529738</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.1232288086559916</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BE3" t="n">
-        <v>0.1274275497058414</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
       <c r="BG3" t="n">
-        <v>0.1239978030397312</v>
+        <v>0.1225040537262849</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.116766363338641</v>
+        <v>0.1144401652424383</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.09489915749074032</v>
+        <v>0.09588373864133763</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.09364946762180386</v>
+        <v>0.08931100987019884</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.06553413128133431</v>
+        <v>0.06529991439091037</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.05471155963027138</v>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BQ3" t="n">
-        <v>0.05567742264246246</v>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
       <c r="BS3" t="n">
-        <v>0.0532613474263108</v>
+        <v>0.05424052787596987</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04580742846701123</v>
+        <v>0.04693059412402582</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03856354619152582</v>
+        <v>0.04016811456171775</v>
       </c>
     </row>
     <row r="4">
@@ -1385,100 +1385,100 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.237220935118894</v>
+        <v>1.271675744193238</v>
       </c>
       <c r="L4" t="n">
-        <v>1.498651046638156</v>
+        <v>1.478288609708239</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2680120328378119</v>
+        <v>0.2741545010813485</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2501587288430607</v>
+        <v>0.2508304135683411</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4818292383191272</v>
+        <v>0.4750150853503105</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5320369154203165</v>
+        <v>0.5422801049593369</v>
       </c>
       <c r="R4" t="n">
-        <v>1.144586802678214</v>
+        <v>1.176662214338839</v>
       </c>
       <c r="S4" t="n">
-        <v>1.665413197321786</v>
+        <v>1.673337785661161</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3630224530485811</v>
+        <v>0.3691979210807239</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2329533347182887</v>
+        <v>0.2472310721662867</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4040242122331302</v>
+        <v>0.3835710067529895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5409502473718995</v>
+        <v>0.5111620691226417</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5161628141177554</v>
+        <v>0.5187849183743994</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3014030846565391</v>
+        <v>0.3138911221839645</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2777421186142909</v>
+        <v>0.2779263444531562</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4208547967291699</v>
+        <v>0.4081825333628791</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5151213049396861</v>
+        <v>0.5185343946806951</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4848786950603139</v>
+        <v>0.4814656053193049</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5632383534862582</v>
+        <v>0.5675592829101694</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4367616465137418</v>
+        <v>0.4324407170898306</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.299705</v>
+        <v>0.312675</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.27666</v>
+        <v>0.277075</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.423635</v>
+        <v>0.41025</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.516615</v>
+        <v>0.51969</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.56403</v>
+        <v>0.567785</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.235795</v>
+        <v>1.27073</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.505905</v>
+        <v>1.483755</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.7417</v>
+        <v>2.754485</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.309613442866263</v>
+        <v>0.3173538533567839</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2510326883421982</v>
+        <v>0.2563446267988258</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.439353868791539</v>
+        <v>0.4263015198443904</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.439353868791539</v>
+        <v>0.4263015198443904</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>3.731175758833007</v>
+        <v>3.647578267202241</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.309613442866263</v>
+        <v>0.3173538533567839</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04160141002845097</v>
+        <v>0.04319935227543542</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1552221726314287</v>
+        <v>0.1575730185170918</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3.731175758833007</v>
+        <v>3.647578267202241</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.309613442866263</v>
+        <v>0.3173538533567839</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.04160141002845097</v>
+        <v>0.04319935227543542</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1552221726314287</v>
+        <v>0.1575730185170918</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1322411556511845</v>
+        <v>0.132200840190159</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>0.09008333923876677</v>
+        <v>0.08883227102135055</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1547,23 +1547,23 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>0.08514684346645482</v>
+        <v>0.08248899535183701</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.07641663719626898</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BK4" t="n">
-        <v>0.07685940954274463</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="BM4" t="n">
-        <v>0.07436887557089167</v>
+        <v>0.07594843592644018</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>0.07281103696334557</v>
+        <v>0.06985449822958331</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>0.06819637219196549</v>
+        <v>0.0692801981387091</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="BS4" t="n">
-        <v>0.05572649660580981</v>
+        <v>0.05648292217972568</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.04962387724461902</v>
+        <v>0.05169263748257581</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04500116354494597</v>
+        <v>0.04377324480845926</v>
       </c>
     </row>
     <row r="5">
@@ -1656,100 +1656,100 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.36364417741886</v>
+        <v>1.336837960804804</v>
       </c>
       <c r="L5" t="n">
-        <v>1.030642990517408</v>
+        <v>0.9949487832789894</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5963078289587146</v>
+        <v>0.567339237753298</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2320120351398345</v>
+        <v>0.2471486401506704</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1716801359014509</v>
+        <v>0.1855121220960316</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4597545631199901</v>
+        <v>0.4363677867935911</v>
       </c>
       <c r="R5" t="n">
-        <v>1.706035766783836</v>
+        <v>1.608892852534053</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8039642332161636</v>
+        <v>0.8111071474659468</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2837902134000956</v>
+        <v>0.3189700689910568</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4038521275023543</v>
+        <v>0.3387407750760445</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3123576590975499</v>
+        <v>0.3422891559328987</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3698571726985551</v>
+        <v>0.3703841348549419</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4406702200369585</v>
+        <v>0.4401014652971763</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4315260930084526</v>
+        <v>0.4325137982219593</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2978552985072238</v>
+        <v>0.3019993013513961</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2706186084843235</v>
+        <v>0.2654869004266449</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4287978340453331</v>
+        <v>0.4123724372160993</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5712021659546669</v>
+        <v>0.5876275627839007</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4915558342206369</v>
+        <v>0.4776227658137502</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.508444165779363</v>
+        <v>0.5223772341862498</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.43119</v>
+        <v>0.43219</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.297365</v>
+        <v>0.301375</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.271445</v>
+        <v>0.266435</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.428755</v>
+        <v>0.412475</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.49076</v>
+        <v>0.47737</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.363605</v>
+        <v>1.33672</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.03096</v>
+        <v>0.99691</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.394565</v>
+        <v>2.33363</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.4457312295256325</v>
+        <v>0.4467036688036789</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.3086168833085638</v>
+        <v>0.2929185526747328</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.2456518871658037</v>
+        <v>0.2603777785215884</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.4457312295256325</v>
+        <v>0.4467036688036789</v>
       </c>
       <c r="AS5" t="b">
         <v>1</v>
@@ -1768,33 +1768,33 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>5.824785696663402</v>
+        <v>5.39048332098936</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2456518871658037</v>
+        <v>0.2603777785215884</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.07397175126435285</v>
+        <v>0.07486565642555681</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.4308695987217455</v>
+        <v>0.4035620722768838</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4.310121237449154</v>
+        <v>5.39048332098936</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.3086168833085638</v>
+        <v>0.2603777785215884</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.07660484816872931</v>
+        <v>0.07486565642555681</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.3301761829836083</v>
+        <v>0.4035620722768838</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>0.1410510740149174</v>
+        <v>0.1420987135521884</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>0.1115929527004759</v>
+        <v>0.1169184160186807</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
@@ -1818,23 +1818,23 @@
         </is>
       </c>
       <c r="BI5" t="n">
-        <v>0.1040605390232446</v>
+        <v>0.1100401430063304</v>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.0867851681735656</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BK5" t="n">
-        <v>0.08742885263596308</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
       <c r="BM5" t="n">
-        <v>0.08482942535908738</v>
+        <v>0.08634679748095157</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="BO5" t="n">
-        <v>0.08121068561073895</v>
+        <v>0.08371342860449917</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="BQ5" t="n">
-        <v>0.06607877306292124</v>
+        <v>0.06426406461557246</v>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="BS5" t="n">
-        <v>0.04845748924620263</v>
+        <v>0.04807169342863675</v>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
@@ -1866,15 +1866,15 @@
         </is>
       </c>
       <c r="BU5" t="n">
-        <v>0.04505396706911738</v>
+        <v>0.04295532054685504</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.03974061527848087</v>
+        <v>0.03867256908308382</v>
       </c>
     </row>
     <row r="6">
@@ -1927,10 +1927,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1.193991482618175</v>
+        <v>1.331095796987464</v>
       </c>
       <c r="L6" t="n">
-        <v>1.107211750699903</v>
+        <v>1.156170140995051</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -1942,73 +1942,73 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>0.2985567417222862</v>
+        <v>0.3027676726870674</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2636421922574465</v>
+        <v>0.2882745866063475</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4378010660202674</v>
+        <v>0.4089577407065851</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4839281583348652</v>
+        <v>0.3980861747734591</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5504750831556224</v>
+        <v>0.4846199380546848</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3665544450783714</v>
+        <v>0.3941354300915619</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3097373891325019</v>
+        <v>0.2951770971329929</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3237081657891268</v>
+        <v>0.3106874727754449</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4042801760772498</v>
+        <v>0.4529161454891872</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5957198239227501</v>
+        <v>0.5470838545108128</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4798880327888939</v>
+        <v>0.5170547769368544</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.5201119672111061</v>
+        <v>0.4829452230631456</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.36516</v>
+        <v>0.393925</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.308805</v>
+        <v>0.29488</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.326035</v>
+        <v>0.311195</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.404595</v>
+        <v>0.452805</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.481035</v>
+        <v>0.51641</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.192865</v>
+        <v>1.33102</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.11152</v>
+        <v>1.15669</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.304385</v>
+        <v>2.48771</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.3291557082325245</v>
+        <v>0.34388316351909</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2843850308512214</v>
+        <v>0.291380716343338</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.386459260916254</v>
+        <v>0.3647361201375721</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>0.386459260916254</v>
+        <v>0.3647361201375721</v>
       </c>
       <c r="AS6" t="b">
         <v>0</v>
@@ -2037,39 +2037,39 @@
         </is>
       </c>
       <c r="BE6" t="n">
-        <v>0.1456212558220477</v>
+        <v>0.1407401366357428</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.09786872101622053</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BG6" t="n">
-        <v>0.1133765861998616</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
       <c r="BI6" t="n">
-        <v>0.106325969618075</v>
+        <v>0.09593153354868951</v>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.08515391106512664</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BK6" t="n">
-        <v>0.09763599563837311</v>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="BM6" t="n">
-        <v>0.0790320632453124</v>
+        <v>0.08332593100944595</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="BO6" t="n">
-        <v>0.07328798436265815</v>
+        <v>0.07396342891718614</v>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="BQ6" t="n">
-        <v>0.07137935737708144</v>
+        <v>0.07365171270712756</v>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="BS6" t="n">
-        <v>0.06138065926731141</v>
+        <v>0.05556581959358613</v>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="BU6" t="n">
-        <v>0.0437526145536339</v>
+        <v>0.04922620468122375</v>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="BW6" t="n">
-        <v>0.03145453678954797</v>
+        <v>0.03778267103861145</v>
       </c>
     </row>
     <row r="7">
@@ -2162,10 +2162,10 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7324183241207968</v>
+        <v>0.8282249994906729</v>
       </c>
       <c r="L7" t="n">
-        <v>2.376531082963624</v>
+        <v>2.355124820282166</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -2177,73 +2177,73 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>0.06386189247320018</v>
+        <v>0.0499901391751393</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1174735736916971</v>
+        <v>0.1480287143172439</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8186645338351027</v>
+        <v>0.8019811465076168</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5664932313129929</v>
+        <v>0.588571727409802</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5306670086123414</v>
+        <v>0.5470721437378185</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08889030067591733</v>
+        <v>0.1062458958447988</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1790343392141745</v>
+        <v>0.1875619797469355</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7320753601099078</v>
+        <v>0.706192124408266</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6007552249093393</v>
+        <v>0.6165965253955854</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3992447750906607</v>
+        <v>0.3834034746044146</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.4788005391190281</v>
+        <v>0.517823767686544</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.5211994608809719</v>
+        <v>0.482176232313456</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.08925</v>
+        <v>0.10594</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.178615</v>
+        <v>0.18722</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.732135</v>
+        <v>0.70684</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.59951</v>
+        <v>0.61568</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.478775</v>
+        <v>0.51789</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.73325</v>
+        <v>0.828265</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.37261</v>
+        <v>2.35725</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.10586</v>
+        <v>3.185515</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.07512467616442289</v>
+        <v>0.07530522967648605</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1451759181768119</v>
+        <v>0.1658186837606051</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.7796994056587652</v>
+        <v>0.7588760865629087</v>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="AR7" t="n">
-        <v>0.7796994056587652</v>
+        <v>0.7588760865629087</v>
       </c>
       <c r="AS7" t="b">
         <v>0</v>
@@ -2272,31 +2272,31 @@
         </is>
       </c>
       <c r="BE7" t="n">
-        <v>0.1260882346660777</v>
+        <v>0.11494826377305</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.09520302570488808</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
           <t>0-3</t>
         </is>
       </c>
-      <c r="BG7" t="n">
-        <v>0.09988420295998175</v>
-      </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="n">
+        <v>0.09023916968675048</v>
+      </c>
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BI7" t="n">
-        <v>0.09833938394595655</v>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="BK7" t="n">
-        <v>0.09234933352547839</v>
+        <v>0.08953067819983314</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>0.0854895335526997</v>
+        <v>0.08893229553992818</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="BO7" t="n">
-        <v>0.07315702053809135</v>
+        <v>0.07473833626784765</v>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="BQ7" t="n">
-        <v>0.05934447825786095</v>
+        <v>0.05313112707273002</v>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="BS7" t="n">
-        <v>0.05242137471781484</v>
+        <v>0.04953284703900651</v>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="BU7" t="n">
-        <v>0.04346498331144558</v>
+        <v>0.0440045276927507</v>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="BW7" t="n">
-        <v>0.03381917204720169</v>
+        <v>0.03942476295797073</v>
       </c>
     </row>
   </sheetData>
